--- a/data/industry/Logistics/Logistic manager index.xlsx
+++ b/data/industry/Logistics/Logistic manager index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/Logistics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13E9F13-CF67-7846-AF3F-061425F8858F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749C9E12-452F-4AD2-92D1-C8F628554BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25300" yWindow="600" windowWidth="25900" windowHeight="26380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LMI" sheetId="1" r:id="rId1"/>
@@ -257,10 +257,10 @@
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -278,7 +278,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7280,7 +7280,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14440,22 +14440,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.44140625" style="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.1640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.109375" style="13" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
@@ -19472,13 +19472,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF85ECF-5DA2-D446-A4EF-6579CB12CAA0}">
   <dimension ref="A1:N94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" style="17" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" style="17" customWidth="1"/>
     <col min="6" max="13" width="9" style="18"/>
     <col min="14" max="16384" width="9" style="8"/>
   </cols>
@@ -23469,9 +23469,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E55565-0C4A-423B-A75C-9DC33F6F8AE5}">
   <dimension ref="B2:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11">
@@ -23510,7 +23510,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A53279-3D0D-4247-AAE5-068BE8617509}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="4"/>
   </cols>

--- a/data/industry/Logistics/Logistic manager index.xlsx
+++ b/data/industry/Logistics/Logistic manager index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/Logistics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D3C6EC-BA50-274C-9238-A4F2F51ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A755FC-ADB6-481D-AB65-4CABFE3F1943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20720" yWindow="4640" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LMI" sheetId="1" r:id="rId1"/>
@@ -282,10 +282,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -303,7 +303,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6341,7 +6341,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-0E98-FE47-BBE2-4ECC5954C1C9}"/>
@@ -7305,7 +7305,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14465,15 +14465,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="11" customWidth="1"/>
-    <col min="6" max="13" width="11.1640625" style="12" customWidth="1"/>
-    <col min="14" max="14" width="21.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="11" customWidth="1"/>
+    <col min="6" max="13" width="11.109375" style="12" customWidth="1"/>
+    <col min="14" max="14" width="21.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
@@ -19490,15 +19490,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF85ECF-5DA2-D446-A4EF-6579CB12CAA0}">
   <dimension ref="A1:N94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" style="15" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="10.6640625" style="16" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="9.6640625" style="16" bestFit="1" customWidth="1"/>
@@ -23491,9 +23491,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E55565-0C4A-423B-A75C-9DC33F6F8AE5}">
   <dimension ref="B2:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11">
@@ -23532,7 +23532,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A53279-3D0D-4247-AAE5-068BE8617509}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="4"/>
   </cols>
